--- a/_qfield_skeleton/_pdg/liste.xlsx
+++ b/_qfield_skeleton/_pdg/liste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\git\q-sync\_qfield_skeleton\_pdg\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F319BF4-987B-4F92-ABAA-9C9028F2535F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD9ADED-B248-4E0A-B6F6-90D387AAFE48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11205" xr2:uid="{3895A33C-B4B1-4D69-BED9-60DAD710A78D}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>PDG</t>
   </si>
@@ -42,9 +42,6 @@
     <t>cassini</t>
   </si>
   <si>
-    <t>etat-major</t>
-  </si>
-  <si>
     <t>geologie</t>
   </si>
   <si>
@@ -67,6 +64,60 @@
   </si>
   <si>
     <t>inventaire_national_patrimoine_geologique</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>AN-IGNF_GEOGRAPHICALGRIDSYSTEMS.CASSINI</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Carte de Cassini</t>
+  </si>
+  <si>
+    <t>Url</t>
+  </si>
+  <si>
+    <t>https://data.geopf.fr/wmts?SERVICE=WMTS&amp;VERSION=1.0.0&amp;REQUEST=GetCapabilities</t>
+  </si>
+  <si>
+    <t>Géoplateforme</t>
+  </si>
+  <si>
+    <t>SCAN_H_RELIEF_GEOL50_SCAN</t>
+  </si>
+  <si>
+    <t>Carte d'assemblage des cartes géologiques au 1/50 000e - MNT harmonisé</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>wms</t>
+  </si>
+  <si>
+    <t>wfs</t>
+  </si>
+  <si>
+    <t>znieff1</t>
+  </si>
+  <si>
+    <t>znieff2</t>
+  </si>
+  <si>
+    <t>zps</t>
+  </si>
+  <si>
+    <t>PATRINAT : ZNIEFF1</t>
+  </si>
+  <si>
+    <t>PATRINAT : ZNIEFF2</t>
+  </si>
+  <si>
+    <t>PATRINAT : ZPS</t>
   </si>
 </sst>
 </file>
@@ -418,14 +469,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE91F977-33D9-49C9-AA0E-DFF3EC9B319B}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="47.140625" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" customWidth="1"/>
+    <col min="2" max="3" width="47.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="47.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,60 +487,160 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>12</v>
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
